--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487704_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487704_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7945</v>
+        <v>4.0487</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4954</v>
+        <v>2.3953</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2991</v>
+        <v>1.6534</v>
       </c>
       <c r="G2" t="n">
         <v>3.952</v>
@@ -610,13 +610,13 @@
         <v>3.1045</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7575</v>
+        <v>-0.5033</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1189</v>
+        <v>-0.219</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6385999999999999</v>
+        <v>-0.2843</v>
       </c>
       <c r="V2" t="n">
         <v>-0.5642</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8246</v>
+        <v>0.7235</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1311</v>
+        <v>1.03</v>
       </c>
       <c r="F3" t="n">
         <v>-0.3065</v>
@@ -688,10 +688,10 @@
         <v>1.1642</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4199</v>
+        <v>0.3188</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2146</v>
+        <v>0.1135</v>
       </c>
       <c r="U3" t="n">
         <v>0.2053</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.123</v>
+        <v>0.541</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.1478</v>
+        <v>-1.6473</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0248</v>
+        <v>2.1884</v>
       </c>
       <c r="G4" t="n">
         <v>3.0397</v>
@@ -766,13 +766,13 @@
         <v>1.9403</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2985</v>
+        <v>-0.6345</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6662</v>
+        <v>-0.1657</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6323</v>
+        <v>-0.4688</v>
       </c>
       <c r="V4" t="n">
         <v>-0.894</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.142</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-4.18</v>
+        <v>-4.2801</v>
       </c>
       <c r="F5" t="n">
-        <v>4.038</v>
+        <v>3.7655</v>
       </c>
       <c r="G5" t="n">
         <v>2.6002</v>
@@ -844,13 +844,13 @@
         <v>2.5224</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5563</v>
+        <v>0.1837</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1233</v>
+        <v>0.0232</v>
       </c>
       <c r="U5" t="n">
-        <v>0.433</v>
+        <v>0.1604</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. PEREZ BERNABEU</t>
+          <t>I. BLANCO-ARGIBAY GONZALEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1437</v>
+        <v>-0.6831</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.0817</v>
+        <v>-1.028</v>
       </c>
       <c r="F6" t="n">
-        <v>3.9381</v>
+        <v>0.3449</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.9233</v>
+        <v>1.4267</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.3292</v>
+        <v>1.1303</v>
       </c>
       <c r="I6" t="n">
-        <v>0.406</v>
+        <v>0.2964</v>
       </c>
       <c r="J6" t="n">
-        <v>-4.366</v>
+        <v>1.7625</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.5086</v>
+        <v>1.7219</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.8574</v>
+        <v>0.0406</v>
       </c>
       <c r="M6" t="n">
-        <v>1.4427</v>
+        <v>-0.3358</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8206</v>
+        <v>-0.5916</v>
       </c>
       <c r="O6" t="n">
-        <v>2.2633</v>
+        <v>0.2558</v>
       </c>
       <c r="P6" t="n">
-        <v>3.1045</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1045</v>
+        <v>1.5523</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6169</v>
+        <v>0.1424</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0022</v>
+        <v>-0.1621</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6147</v>
+        <v>0.3045</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9418</v>
+        <v>-0.894</v>
       </c>
       <c r="W6" t="n">
         <v>0.2821</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2239</v>
+        <v>-1.1761</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. BLANCO-ARGIBAY GONZALEZ</t>
+          <t>E. PEREZ BERNABEU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4199</v>
+        <v>-0.889</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2282</v>
+        <v>-4.2819</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8083</v>
+        <v>3.393</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4267</v>
+        <v>-2.9233</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1303</v>
+        <v>-3.3292</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2964</v>
+        <v>0.406</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7625</v>
+        <v>-4.366</v>
       </c>
       <c r="K7" t="n">
-        <v>1.7219</v>
+        <v>-2.5086</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0406</v>
+        <v>-1.8574</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3358</v>
+        <v>1.4427</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5916</v>
+        <v>-0.8206</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2558</v>
+        <v>2.2633</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.3582</v>
+        <v>3.1045</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9105</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5523</v>
+        <v>3.1045</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4056</v>
+        <v>-0.1284</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3623</v>
+        <v>-0.198</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7679</v>
+        <v>0.0696</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.894</v>
+        <v>-0.9418</v>
       </c>
       <c r="W7" t="n">
         <v>0.2821</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1761</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.3966</v>
+        <v>-1.3872</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2697</v>
+        <v>0.8703</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.6663</v>
+        <v>-2.2575</v>
       </c>
       <c r="G8" t="n">
         <v>0.5763</v>
@@ -1078,13 +1078,13 @@
         <v>1.3582</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2909</v>
+        <v>-0.2815</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0296</v>
+        <v>-0.429</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2613</v>
+        <v>0.1475</v>
       </c>
       <c r="V8" t="n">
         <v>-2.0701</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.92</v>
+        <v>-3.3655</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.4552</v>
+        <v>-5.255</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5352</v>
+        <v>1.8895</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7327</v>
@@ -1156,13 +1156,13 @@
         <v>3.6866</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1097</v>
+        <v>-0.5552</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5429</v>
+        <v>-0.3427</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5668</v>
+        <v>-0.2125</v>
       </c>
       <c r="V9" t="n">
         <v>-1.8836</v>
@@ -1189,7 +1189,7 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.526099999999999</v>
+        <v>-1.5262</v>
       </c>
       <c r="E10" t="n">
         <v>-12.1967</v>
@@ -1234,13 +1234,13 @@
         <v>18.433</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4579</v>
+        <v>-1.458</v>
       </c>
       <c r="T10" t="n">
         <v>-1.3798</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.07809999999999973</v>
+        <v>-0.07829999999999998</v>
       </c>
       <c r="V10" t="n">
         <v>-8.189500000000001</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4.2468</v>
+        <v>3.3737</v>
       </c>
       <c r="E11" t="n">
-        <v>2.7019</v>
+        <v>2.1013</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5449</v>
+        <v>1.2724</v>
       </c>
       <c r="G11" t="n">
         <v>2.6265</v>
@@ -1312,13 +1312,13 @@
         <v>1.3582</v>
       </c>
       <c r="S11" t="n">
-        <v>1.2607</v>
+        <v>0.3875</v>
       </c>
       <c r="T11" t="n">
-        <v>0.729</v>
+        <v>0.1284</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5317</v>
+        <v>0.2591</v>
       </c>
       <c r="V11" t="n">
         <v>0.9418</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. MANZANERO CAMACHO</t>
+          <t>E. PASCUAL COZAR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.668</v>
+        <v>3.0841</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3685</v>
+        <v>0.7352</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0365</v>
+        <v>2.3489</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.5657</v>
+        <v>1.0082</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.2333</v>
+        <v>-0.0824</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.3323</v>
+        <v>1.0905</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.6005</v>
+        <v>0.4101</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.0123</v>
+        <v>0.3872</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.5881</v>
+        <v>0.0228</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.9651999999999999</v>
+        <v>0.5981</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.221</v>
+        <v>-0.4696</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2558</v>
+        <v>1.0677</v>
       </c>
       <c r="P12" t="n">
-        <v>0.194</v>
+        <v>1.1642</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R12" t="n">
         <v>2.1344</v>
       </c>
       <c r="S12" t="n">
-        <v>4.4277</v>
+        <v>0.2521</v>
       </c>
       <c r="T12" t="n">
-        <v>3.2783</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>1.1494</v>
+        <v>0.1806</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6119</v>
+        <v>0.6597</v>
       </c>
       <c r="W12" t="n">
-        <v>0.894</v>
+        <v>1.2239</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2821</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E. PASCUAL COZAR</t>
+          <t>L. GARCIA LARRACHE SEGURA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.656</v>
+        <v>1.9896</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.3659</v>
+        <v>2.3541</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0218</v>
+        <v>-0.3645</v>
       </c>
       <c r="G13" t="n">
-        <v>1.0082</v>
+        <v>0.1512</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0824</v>
+        <v>2.0069</v>
       </c>
       <c r="I13" t="n">
-        <v>1.0905</v>
+        <v>-1.8558</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4101</v>
+        <v>0.9881</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3872</v>
+        <v>2.2821</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0228</v>
+        <v>-1.2941</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5981</v>
+        <v>-0.8369</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4696</v>
+        <v>-0.2752</v>
       </c>
       <c r="O13" t="n">
-        <v>1.0677</v>
+        <v>-0.5617</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1642</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R13" t="n">
         <v>2.1344</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1761</v>
+        <v>-0.3973</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0296</v>
+        <v>-0.5712</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1465</v>
+        <v>0.1739</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6597</v>
+        <v>3.0119</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2239</v>
+        <v>4.8477</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5642</v>
+        <v>-1.8358</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L. GARCIA LARRACHE SEGURA</t>
+          <t>M. KREISLER LORENTE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4525</v>
+        <v>0.9387</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6534</v>
+        <v>-0.168</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.201</v>
+        <v>1.1067</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1512</v>
+        <v>0.3417</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0069</v>
+        <v>1.6008</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.8558</v>
+        <v>-1.259</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9881</v>
+        <v>1.089</v>
       </c>
       <c r="K14" t="n">
-        <v>2.2821</v>
+        <v>1.7919</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.2941</v>
+        <v>-0.7029</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8369</v>
+        <v>-0.7473</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2752</v>
+        <v>-0.1912</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5617</v>
+        <v>-0.5561</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.7761</v>
+        <v>0.7761</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1344</v>
+        <v>1.7463</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9345</v>
+        <v>-0.1792</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2719</v>
+        <v>-0.2869</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3374</v>
+        <v>0.1077</v>
       </c>
       <c r="V14" t="n">
-        <v>3.0119</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>4.8477</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.8358</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. KREISLER LORENTE</t>
+          <t>J. MARTINEZ SANTOS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4382</v>
+        <v>0.5962</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.6685</v>
+        <v>0.2037</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1067</v>
+        <v>0.3925</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3417</v>
+        <v>1.0384</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6008</v>
+        <v>0.5223</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.259</v>
+        <v>0.5161</v>
       </c>
       <c r="J15" t="n">
-        <v>1.089</v>
+        <v>1.0121</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7919</v>
+        <v>1.0298</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.7029</v>
+        <v>-0.0178</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7473</v>
+        <v>0.0263</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1912</v>
+        <v>-0.5075</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5561</v>
+        <v>0.5339</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7761</v>
+        <v>-0.194</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7463</v>
+        <v>0.7761</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6797</v>
+        <v>0.0339</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7874</v>
+        <v>0.1618</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1077</v>
+        <v>-0.1278</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MARTINEZ SANTOS</t>
+          <t>J. LAPASTORA ARACIL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3326</v>
+        <v>0.2766</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1036</v>
+        <v>-0.5672</v>
       </c>
       <c r="F16" t="n">
-        <v>0.229</v>
+        <v>0.8438</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0384</v>
+        <v>-1.6535</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5223</v>
+        <v>-1.857</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5161</v>
+        <v>0.2035</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0121</v>
+        <v>-0.95</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0298</v>
+        <v>-1.5818</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.0178</v>
+        <v>0.6318</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0263</v>
+        <v>-0.7034</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5075</v>
+        <v>-0.2752</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5339</v>
+        <v>-0.4282</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.194</v>
+        <v>0.3881</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7761</v>
+        <v>2.3284</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2297</v>
+        <v>-0.2939</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0617</v>
+        <v>-0.0769</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2914</v>
+        <v>-0.217</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2821</v>
+        <v>1.8358</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2821</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. LAPASTORA ARACIL</t>
+          <t>N. LASUNCION MARIBLANCA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0679</v>
+        <v>-0.8854</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.367</v>
+        <v>-3.3311</v>
       </c>
       <c r="F17" t="n">
-        <v>0.435</v>
+        <v>2.4457</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.6535</v>
+        <v>-1.929</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.857</v>
+        <v>-1.319</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2035</v>
+        <v>-0.61</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.95</v>
+        <v>-2.2717</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.5818</v>
+        <v>-0.8609</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6318</v>
+        <v>-1.4108</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7034</v>
+        <v>0.3427</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2752</v>
+        <v>-0.4581</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4282</v>
+        <v>0.8008</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3881</v>
+        <v>0.7761</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3284</v>
+        <v>1.7463</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5024999999999999</v>
+        <v>0.2675</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1233</v>
+        <v>-0.0892</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6258</v>
+        <v>0.3567</v>
       </c>
       <c r="V17" t="n">
-        <v>1.8358</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. LASUNCION MARIBLANCA</t>
+          <t>D. MANZANERO CAMACHO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.159</v>
+        <v>-1.3429</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.3321</v>
+        <v>-2.6708</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1731</v>
+        <v>1.3279</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.929</v>
+        <v>-3.5657</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.319</v>
+        <v>-1.2333</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.61</v>
+        <v>-2.3323</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.2717</v>
+        <v>-2.6005</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.8609</v>
+        <v>-0.0123</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.4108</v>
+        <v>-2.5881</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3427</v>
+        <v>-0.9651999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4581</v>
+        <v>-1.221</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8008</v>
+        <v>0.2558</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7761</v>
+        <v>0.194</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7463</v>
+        <v>2.1344</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0061</v>
+        <v>1.4168</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0902</v>
+        <v>0.976</v>
       </c>
       <c r="U18" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.4408</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.6119</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.894</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. GARCIA-LARRACHE SEGURA</t>
+          <t>E. MARTINEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.0314</v>
+        <v>-3.1093</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.6663</v>
+        <v>-4.4614</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6348</v>
+        <v>1.3521</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.0379</v>
+        <v>-3.1012</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0117</v>
+        <v>-2.7764</v>
       </c>
       <c r="I19" t="n">
-        <v>-4.0496</v>
+        <v>-0.3248</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.201</v>
+        <v>-2.481</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1534</v>
+        <v>-1.2275</v>
       </c>
       <c r="L19" t="n">
-        <v>-3.3544</v>
+        <v>-1.2535</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8369</v>
+        <v>-0.6202</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1417</v>
+        <v>-1.5489</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6952</v>
+        <v>0.9287</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7761</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q19" t="n">
         <v>-2.9105</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1344</v>
+        <v>1.9403</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2185</v>
+        <v>0.1158</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1189</v>
+        <v>0.0838</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3374</v>
+        <v>0.032</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5642</v>
+        <v>0.8462</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5642</v>
+        <v>0.8462</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. MARTINEZ ALVAREZ</t>
+          <t>J. GARCIA-LARRACHE SEGURA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.1455</v>
+        <v>-3.3951</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.3613</v>
+        <v>-4.8665</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2158</v>
+        <v>1.4713</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.1012</v>
+        <v>-3.0379</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.7764</v>
+        <v>1.0117</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3248</v>
+        <v>-4.0496</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.481</v>
+        <v>-2.201</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.2275</v>
+        <v>1.1534</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2535</v>
+        <v>-3.3544</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6202</v>
+        <v>-0.8369</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.5489</v>
+        <v>-0.1417</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9287</v>
+        <v>-0.6952</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9702</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q20" t="n">
         <v>-2.9105</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9403</v>
+        <v>2.1344</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0796</v>
+        <v>-0.1452</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1839</v>
+        <v>-0.3191</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1043</v>
+        <v>0.1739</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8462</v>
+        <v>0.5642</v>
       </c>
       <c r="W20" t="n">
-        <v>0.8462</v>
+        <v>0.5642</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,28 +2047,28 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.526100000000001</v>
+        <v>1.5262</v>
       </c>
       <c r="E21" t="n">
         <v>-10.6707</v>
       </c>
       <c r="F21" t="n">
-        <v>12.1966</v>
+        <v>12.1968</v>
       </c>
       <c r="G21" t="n">
         <v>-8.1213</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6096999999999997</v>
+        <v>0.6097000000000004</v>
       </c>
       <c r="I21" t="n">
-        <v>-8.731</v>
+        <v>-8.730999999999998</v>
       </c>
       <c r="J21" t="n">
         <v>-4.3155</v>
       </c>
       <c r="K21" t="n">
-        <v>5.610699999999999</v>
+        <v>5.6107</v>
       </c>
       <c r="L21" t="n">
         <v>-9.926400000000001</v>
@@ -2083,7 +2083,7 @@
         <v>1.1955</v>
       </c>
       <c r="P21" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-2.220446049250313e-16</v>
       </c>
       <c r="Q21" t="n">
         <v>-18.4332</v>
@@ -2092,13 +2092,13 @@
         <v>18.4332</v>
       </c>
       <c r="S21" t="n">
-        <v>1.4579</v>
+        <v>1.458</v>
       </c>
       <c r="T21" t="n">
         <v>0.07819999999999988</v>
       </c>
       <c r="U21" t="n">
-        <v>1.3797</v>
+        <v>1.3799</v>
       </c>
       <c r="V21" t="n">
         <v>8.189399999999999</v>
